--- a/www/ig/fhir/eprescription/1.1.0-ballot/ValueSet-fr-additional-action-relationship-type-value-set.xlsx
+++ b/www/ig/fhir/eprescription/1.1.0-ballot/ValueSet-fr-additional-action-relationship-type-value-set.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-10T16:58:35+00:00</t>
+    <t>2026-05-11T06:23:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
